--- a/Codes_2025/Trial 3/Trial3_LSTM_Leaders_Results.xlsx
+++ b/Codes_2025/Trial 3/Trial3_LSTM_Leaders_Results.xlsx
@@ -470,13 +470,13 @@
         <v>2025</v>
       </c>
       <c r="C2" t="n">
-        <v>22.34</v>
+        <v>6.549999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>17.86065101623535</v>
+        <v>2.651774883270264</v>
       </c>
       <c r="E2" t="n">
-        <v>4.479348983764645</v>
+        <v>3.898225116729735</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -494,13 +494,13 @@
         <v>2025</v>
       </c>
       <c r="C3" t="n">
-        <v>35.4</v>
+        <v>69.53000000000007</v>
       </c>
       <c r="D3" t="n">
-        <v>18.9803409576416</v>
+        <v>2.694349527359009</v>
       </c>
       <c r="E3" t="n">
-        <v>16.4196590423584</v>
+        <v>66.83565047264106</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -518,13 +518,13 @@
         <v>2025</v>
       </c>
       <c r="C4" t="n">
-        <v>6.549999999999999</v>
+        <v>21.01</v>
       </c>
       <c r="D4" t="n">
-        <v>18.06757736206055</v>
+        <v>2.896033048629761</v>
       </c>
       <c r="E4" t="n">
-        <v>11.51757736206055</v>
+        <v>18.11396695137024</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -542,13 +542,13 @@
         <v>2025</v>
       </c>
       <c r="C5" t="n">
-        <v>69.53000000000007</v>
+        <v>20.08</v>
       </c>
       <c r="D5" t="n">
-        <v>18.73909187316895</v>
+        <v>2.981366872787476</v>
       </c>
       <c r="E5" t="n">
-        <v>50.79090812683113</v>
+        <v>17.09863312721252</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -566,13 +566,13 @@
         <v>2025</v>
       </c>
       <c r="C6" t="n">
-        <v>21.01</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>20.01977920532227</v>
+        <v>3.044501066207886</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9902207946777359</v>
+        <v>6.315498933792114</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -590,13 +590,13 @@
         <v>2025</v>
       </c>
       <c r="C7" t="n">
-        <v>20.08</v>
+        <v>7.180000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>21.03390693664551</v>
+        <v>3.018102645874023</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9539069366455095</v>
+        <v>4.161897354125977</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -614,13 +614,13 @@
         <v>2025</v>
       </c>
       <c r="C8" t="n">
-        <v>9.359999999999999</v>
+        <v>37.67999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>19.06016540527344</v>
+        <v>3.009930849075317</v>
       </c>
       <c r="E8" t="n">
-        <v>9.700165405273438</v>
+        <v>34.67006915092468</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -638,13 +638,13 @@
         <v>2025</v>
       </c>
       <c r="C9" t="n">
-        <v>7.180000000000001</v>
+        <v>7.73</v>
       </c>
       <c r="D9" t="n">
-        <v>17.69006156921387</v>
+        <v>2.955321788787842</v>
       </c>
       <c r="E9" t="n">
-        <v>10.51006156921387</v>
+        <v>4.774678211212158</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -662,13 +662,13 @@
         <v>2025</v>
       </c>
       <c r="C10" t="n">
-        <v>37.67999999999999</v>
+        <v>6.590000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>18.40886878967285</v>
+        <v>2.737058162689209</v>
       </c>
       <c r="E10" t="n">
-        <v>19.27113121032714</v>
+        <v>3.852941837310792</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -686,13 +686,13 @@
         <v>2025</v>
       </c>
       <c r="C11" t="n">
-        <v>7.73</v>
+        <v>10.19</v>
       </c>
       <c r="D11" t="n">
-        <v>13.58598613739014</v>
+        <v>3.099096298217773</v>
       </c>
       <c r="E11" t="n">
-        <v>5.855986137390137</v>
+        <v>7.090903701782224</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -710,13 +710,13 @@
         <v>2025</v>
       </c>
       <c r="C12" t="n">
-        <v>6.590000000000001</v>
+        <v>37.58000000000002</v>
       </c>
       <c r="D12" t="n">
-        <v>14.97559833526611</v>
+        <v>2.931546926498413</v>
       </c>
       <c r="E12" t="n">
-        <v>8.385598335266113</v>
+        <v>34.64845307350161</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -734,13 +734,13 @@
         <v>2025</v>
       </c>
       <c r="C13" t="n">
-        <v>10.19</v>
+        <v>10.68</v>
       </c>
       <c r="D13" t="n">
-        <v>16.32448577880859</v>
+        <v>2.037041664123535</v>
       </c>
       <c r="E13" t="n">
-        <v>6.134485778808596</v>
+        <v>8.642958335876463</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -758,13 +758,13 @@
         <v>2025</v>
       </c>
       <c r="C14" t="n">
-        <v>37.58000000000002</v>
+        <v>7.740000000000002</v>
       </c>
       <c r="D14" t="n">
-        <v>21.16464614868164</v>
+        <v>1.999727606773376</v>
       </c>
       <c r="E14" t="n">
-        <v>16.41535385131838</v>
+        <v>5.740272393226626</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>

--- a/Codes_2025/Trial 3/Trial3_LSTM_Leaders_Results.xlsx
+++ b/Codes_2025/Trial 3/Trial3_LSTM_Leaders_Results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,10 +473,10 @@
         <v>6.549999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>2.651774883270264</v>
+        <v>1.089541077613831</v>
       </c>
       <c r="E2" t="n">
-        <v>3.898225116729735</v>
+        <v>5.460458922386168</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -497,10 +497,10 @@
         <v>69.53000000000007</v>
       </c>
       <c r="D3" t="n">
-        <v>2.694349527359009</v>
+        <v>1.066940069198608</v>
       </c>
       <c r="E3" t="n">
-        <v>66.83565047264106</v>
+        <v>68.46305993080146</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -518,13 +518,13 @@
         <v>2025</v>
       </c>
       <c r="C4" t="n">
-        <v>21.01</v>
+        <v>37.81</v>
       </c>
       <c r="D4" t="n">
-        <v>2.896033048629761</v>
+        <v>1.16821300983429</v>
       </c>
       <c r="E4" t="n">
-        <v>18.11396695137024</v>
+        <v>36.64178699016571</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -542,13 +542,13 @@
         <v>2025</v>
       </c>
       <c r="C5" t="n">
-        <v>20.08</v>
+        <v>21.01</v>
       </c>
       <c r="D5" t="n">
-        <v>2.981366872787476</v>
+        <v>1.117696762084961</v>
       </c>
       <c r="E5" t="n">
-        <v>17.09863312721252</v>
+        <v>19.89230323791504</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -559,20 +559,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>2025</v>
       </c>
       <c r="C6" t="n">
-        <v>9.359999999999999</v>
+        <v>20.08</v>
       </c>
       <c r="D6" t="n">
-        <v>3.044501066207886</v>
+        <v>1.209541440010071</v>
       </c>
       <c r="E6" t="n">
-        <v>6.315498933792114</v>
+        <v>18.87045855998993</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -583,20 +583,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>2025</v>
       </c>
       <c r="C7" t="n">
-        <v>7.180000000000001</v>
+        <v>28.09</v>
       </c>
       <c r="D7" t="n">
-        <v>3.018102645874023</v>
+        <v>1.824130773544312</v>
       </c>
       <c r="E7" t="n">
-        <v>4.161897354125977</v>
+        <v>26.26586922645568</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -607,20 +607,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>2025</v>
       </c>
       <c r="C8" t="n">
-        <v>37.67999999999999</v>
+        <v>6.81</v>
       </c>
       <c r="D8" t="n">
-        <v>3.009930849075317</v>
+        <v>1.022858381271362</v>
       </c>
       <c r="E8" t="n">
-        <v>34.67006915092468</v>
+        <v>5.787141618728637</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -631,20 +631,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>2025</v>
       </c>
       <c r="C9" t="n">
-        <v>7.73</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>2.955321788787842</v>
+        <v>0.9746938943862915</v>
       </c>
       <c r="E9" t="n">
-        <v>4.774678211212158</v>
+        <v>8.385306105613708</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -655,20 +655,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>2025</v>
       </c>
       <c r="C10" t="n">
-        <v>6.590000000000001</v>
+        <v>7.180000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>2.737058162689209</v>
+        <v>1.236179828643799</v>
       </c>
       <c r="E10" t="n">
-        <v>3.852941837310792</v>
+        <v>5.943820171356202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -679,20 +679,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>2025</v>
       </c>
       <c r="C11" t="n">
-        <v>10.19</v>
+        <v>37.67999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>3.099096298217773</v>
+        <v>1.175017595291138</v>
       </c>
       <c r="E11" t="n">
-        <v>7.090903701782224</v>
+        <v>36.50498240470885</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -703,20 +703,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>2025</v>
       </c>
       <c r="C12" t="n">
-        <v>37.58000000000002</v>
+        <v>7.73</v>
       </c>
       <c r="D12" t="n">
-        <v>2.931546926498413</v>
+        <v>1.196748733520508</v>
       </c>
       <c r="E12" t="n">
-        <v>34.64845307350161</v>
+        <v>6.533251266479492</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -727,20 +727,20 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>2025</v>
       </c>
       <c r="C13" t="n">
-        <v>10.68</v>
+        <v>24.26000000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>2.037041664123535</v>
+        <v>1.208151817321777</v>
       </c>
       <c r="E13" t="n">
-        <v>8.642958335876463</v>
+        <v>23.05184818267823</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -751,22 +751,118 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C14" t="n">
+        <v>6.590000000000001</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.686741232872009</v>
+      </c>
+      <c r="E14" t="n">
+        <v>4.903258767127991</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Leaders</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C15" t="n">
+        <v>10.19</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.201385855674744</v>
+      </c>
+      <c r="E15" t="n">
+        <v>8.988614144325254</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Leaders</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C16" t="n">
+        <v>37.58000000000002</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.457441926002502</v>
+      </c>
+      <c r="E16" t="n">
+        <v>36.12255807399752</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Leaders</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C17" t="n">
+        <v>10.68</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.347021818161011</v>
+      </c>
+      <c r="E17" t="n">
+        <v>8.332978181838987</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Leaders</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>Sweden</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C14" t="n">
+      <c r="B18" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C18" t="n">
         <v>7.740000000000002</v>
       </c>
-      <c r="D14" t="n">
-        <v>1.999727606773376</v>
-      </c>
-      <c r="E14" t="n">
-        <v>5.740272393226626</v>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="D18" t="n">
+        <v>1.762341499328613</v>
+      </c>
+      <c r="E18" t="n">
+        <v>5.977658500671389</v>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>Leaders</t>
         </is>
